--- a/Vanco/data/Vanco Stats_formatted.xlsx
+++ b/Vanco/data/Vanco Stats_formatted.xlsx
@@ -595,7 +595,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>747</v>
+        <v>570</v>
       </c>
     </row>
     <row r="12">
@@ -775,7 +775,7 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D21" t="n">
-        <v>570</v>
+        <v>747</v>
       </c>
     </row>
     <row r="22">
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D9" t="n">
         <v>570</v>
@@ -2431,7 +2431,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12">
@@ -2485,7 +2485,7 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
